--- a/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_info.xlsx
+++ b/XD_JIG/XD12/XD12R_GT1009A0R0/Docs/xd12r_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12R_GT1009A0R0\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592BBDFC-897B-4F02-8026-4DA2A0E6A903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19604666-C85B-4472-A365-2DCF315810DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{1EECCE5F-2B3C-4FB1-86A3-4A5E96E35C38}"/>
+    <workbookView xWindow="48045" yWindow="5235" windowWidth="21600" windowHeight="11175" xr2:uid="{1EECCE5F-2B3C-4FB1-86A3-4A5E96E35C38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,67 +36,83 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>MHz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>us</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>MCLK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Vsync</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Hz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCLK_CNT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>V_MASK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2분주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCLK 기준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SV_MASK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYSYNC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LD RGB Mode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>User Input</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVSYNC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ea</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPWM_DIV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCLK_LOCK_CNT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Calculate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -110,13 +126,33 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -133,8 +169,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -471,145 +522,210 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D8A149-062A-4BD9-BCA8-F95A52D0EBAF}">
-  <dimension ref="B2:F20"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:O14"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.6640625" style="2"/>
+    <col min="14" max="14" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2">
+        <v>120</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3">
+        <f>1000000/D3</f>
+        <v>8333.3333333333339</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="N4" s="2">
+        <v>500</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="N5" s="2">
+        <f>1/N4</f>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B6" s="1"/>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B7" s="1"/>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2">
+        <f>(D7+1)*2^14*3</f>
+        <v>442368</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5">
+        <f>ROUND(D9*1.001, 0)</f>
+        <v>442810</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B10" s="1"/>
+      <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>51.118079999999992</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D10" s="3">
+        <f>D3*F9</f>
+        <v>53137200</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E2">
-        <f>1/C2</f>
-        <v>1.9562550080128208E-2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>120</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <f>1000000/C3</f>
-        <v>8333.3333333333339</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="D4" t="s">
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B11" s="1"/>
+      <c r="C11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4">
-        <f>E3/E2</f>
-        <v>425984</v>
-      </c>
-      <c r="F4">
-        <f>E4*1.001</f>
-        <v>426409.98399999994</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
+      <c r="D11" s="3">
+        <f>D4*F10/2</f>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="C9">
-        <f>C8/E2</f>
-        <v>766.77119999999991</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="C10">
-        <f>C9/2</f>
-        <v>383.38559999999995</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>20.5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="C13">
-        <f>C12/E2</f>
-        <v>1047.9206399999998</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="C14">
-        <f>C13/2</f>
-        <v>523.96031999999991</v>
-      </c>
-      <c r="D14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20">
-        <v>8</v>
+      <c r="D12" s="3">
+        <f>D5*F10/2</f>
+        <v>553.5</v>
+      </c>
+      <c r="I12" s="2">
+        <v>50</v>
+      </c>
+      <c r="J12" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="I13" s="2">
+        <f>I12*1000000/120</f>
+        <v>416666.66666666669</v>
+      </c>
+      <c r="J13" s="2">
+        <f>J12*1000000/120</f>
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="I14" s="2">
+        <f>I12/64*1000</f>
+        <v>781.25</v>
+      </c>
+      <c r="J14" s="2">
+        <f>J12/64*1000</f>
+        <v>796.875</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <mergeCells count="3">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B9:B12"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>